--- a/Work_description.xlsx
+++ b/Work_description.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\000python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C11A4C2B-F016-4D27-9E0A-DA78767FE9B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{242A8453-2E8B-4346-B05C-659C5EC951BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{6C5289FA-593B-4791-BC92-F44A7D978296}"/>
   </bookViews>
@@ -390,30 +390,12 @@
     <t>Very Low   718.0  818.0</t>
   </si>
   <si>
-    <t>LogReg and others: cv grid search for hyperparameter tuning, scoring = f2 (because imbalanced data and FN is costly: bad customers but classifed good)</t>
-  </si>
-  <si>
-    <t>PSI: not implement since gini is not good</t>
-  </si>
-  <si>
-    <t>LogReg: Feature engineering. Then use features with corr &lt; 0.7, dummies: fine/coarse classing. Gini 0.3055. Scorecard (350-800)</t>
-  </si>
-  <si>
     <t>Check bad rate in 5 groups.</t>
   </si>
   <si>
-    <t>Check bad rate in 5 groups. Notice that 1st group has a bit higher bad rate than 2nd group (0.026 vs 0.022) One of the reason could be: the model recall/f2/.. Is just abt 0.6? (still rooms for wrong predection?)</t>
-  </si>
-  <si>
-    <t>since the results are good enough and not much difference for some models, I choose  randomly XGB for PSI calc and divide risk bands</t>
-  </si>
-  <si>
     <t>5 risk bands are divided using quantile.  Result: table in the right</t>
   </si>
   <si>
-    <t>Good models: all, except GradBoost, AdaBoost and LR</t>
-  </si>
-  <si>
     <t>check corr for features have iv &gt; 0.1 (column AA), then check corr and remove high corr (&gt;0.7). Then it will be the list for LR model (with dummies, later)</t>
   </si>
   <si>
@@ -465,9 +447,6 @@
     <t>hyperparameters tuning with gridsearch, cv = 5, stratified</t>
   </si>
   <si>
-    <t>note: I do not handle cic score (haven't found the way + time…)</t>
-  </si>
-  <si>
     <t>(meaning that if at least 1 dummy has p&lt; 0.05, the feature will be kept)</t>
   </si>
   <si>
@@ -490,6 +469,27 @@
   </si>
   <si>
     <t>cont., fine classing: for features with more than 50 bins-&gt;  50 bins (maximum)</t>
+  </si>
+  <si>
+    <t>PSI: not implement since Gini is not good</t>
+  </si>
+  <si>
+    <t>Gini 0.3055 &lt;0.35 -&gt; model is not good enough. Scorecard: I use the range 350-800</t>
+  </si>
+  <si>
+    <t>LogReg: Feature engineering. Then use features with corr &lt; 0.7, dummies: fine/coarse classing. (List of features chosen by WOE, IV..: see section II)</t>
+  </si>
+  <si>
+    <t>LogReg and others: cv = 5, grid search for hyperparameter tuning, scoring = F2 (because imbalanced data and FN is costly: bad customers but classifed good)</t>
+  </si>
+  <si>
+    <t>since the results are good enough and not much difference for some models, I choose XGB as the representative for PSI calc and divide risk bands</t>
+  </si>
+  <si>
+    <t>Check bad rate in 5 groups. Notice that 1st group has a bit higher bad rate than 2nd group (0.026 vs 0.022) One of the reason could be: the model Recall/F2/.. Is just abt 0.6? (still rooms for wrong predection?)</t>
+  </si>
+  <si>
+    <t>Good models (satisfy Gini&gt; 0.35 and PSI &lt;0.02): all, except GradBoost, AdaBoost and LR</t>
   </si>
 </sst>
 </file>
@@ -1638,7 +1638,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>113</v>
@@ -1646,7 +1646,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="C5" s="13" t="s">
         <v>114</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>115</v>
@@ -1669,14 +1669,14 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>148</v>
+      </c>
       <c r="C8" s="13" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>146</v>
-      </c>
       <c r="C9" s="13" t="s">
         <v>118</v>
       </c>
@@ -1696,41 +1696,41 @@
         <v>2</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C12" s="13"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="C13" s="13"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="C14" s="13"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="C15" s="13"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37" spans="1:2" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -1738,7 +1738,7 @@
         <v>0</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -1753,7 +1753,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -1763,7 +1763,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B43" s="2" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -1823,12 +1823,12 @@
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B57" s="20" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="58" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B58" s="2" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="59" spans="2:2" x14ac:dyDescent="0.25">
@@ -1866,12 +1866,12 @@
     </row>
     <row r="68" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B68" s="2" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="69" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
     </row>
     <row r="70" spans="2:38" x14ac:dyDescent="0.25">
@@ -2431,7 +2431,7 @@
     </row>
     <row r="95" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="K95" s="5">
         <v>32</v>
@@ -2483,7 +2483,7 @@
         <v>1</v>
       </c>
       <c r="B97" s="14" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="K97" s="5">
         <v>16</v>
@@ -2509,7 +2509,7 @@
     </row>
     <row r="98" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K98" s="4">
         <v>20</v>
@@ -2535,7 +2535,7 @@
     </row>
     <row r="99" spans="1:20" ht="24" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="K99" s="5">
         <v>37</v>
@@ -2745,7 +2745,7 @@
     </row>
     <row r="108" spans="1:20" ht="24" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="K108" s="4">
         <v>13</v>
@@ -2771,7 +2771,7 @@
     </row>
     <row r="109" spans="1:20" ht="24" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="K109" s="5">
         <v>24</v>
@@ -2797,7 +2797,7 @@
     </row>
     <row r="110" spans="1:20" ht="24" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="K110" s="4">
         <v>9</v>
@@ -2858,7 +2858,7 @@
         <v>2.3419999999999999E-3</v>
       </c>
     </row>
-    <row r="113" spans="2:17" ht="36" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:17" ht="24" x14ac:dyDescent="0.25">
       <c r="K113" s="5">
         <v>10</v>
       </c>
@@ -2900,7 +2900,7 @@
     </row>
     <row r="115" spans="2:17" ht="24" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="K115" s="4">
         <v>14</v>
@@ -2926,37 +2926,37 @@
         <v>2</v>
       </c>
       <c r="B136" s="14" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B138" s="2" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B139" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B140" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B141" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B142" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C143" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G143" t="s">
         <v>22</v>
@@ -3335,7 +3335,7 @@
     </row>
     <row r="162" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B162" s="19" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C162" s="7" t="s">
         <v>45</v>
